--- a/Wyniki/16.07.2026 NOGI.xlsx
+++ b/Wyniki/16.07.2026 NOGI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dsvcorp-my.sharepoint.com/personal/krzysztof_zaraza_dsv_com/Documents/GitHub/RackIT-1/Wyniki/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{C6CF3B39-96B5-485F-BB8E-383FB494001E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F1E1A0-8020-49FD-B337-907E68141F41}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{C6CF3B39-96B5-485F-BB8E-383FB494001E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E1A93F7-D41F-4B36-BB1B-DF7F8EB67A13}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOGI – Uda · Posladki" sheetId="1" r:id="rId1"/>
@@ -909,27 +909,33 @@
       <c r="G8" s="6">
         <v>75</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="6">
+        <v>6</v>
+      </c>
       <c r="I8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="J8" s="8">
         <v>80</v>
       </c>
-      <c r="K8" s="8"/>
+      <c r="K8" s="8">
+        <v>6</v>
+      </c>
       <c r="L8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="M8" s="10">
         <v>85</v>
       </c>
-      <c r="N8" s="10"/>
+      <c r="N8" s="10">
+        <v>7</v>
+      </c>
       <c r="O8" s="11" t="s">
         <v>22</v>
       </c>
       <c r="P8" t="str">
         <f>IF(N8="","-",IF(ISNUMBER(N8),IF(N8&gt;8,"TAK – dodaj 2,5 kg","NIE – zostan z ciezarem"),"-"))</f>
-        <v>-</v>
+        <v>NIE – zostan z ciezarem</v>
       </c>
       <c r="Q8" s="12" t="s">
         <v>23</v>
@@ -957,27 +963,33 @@
       <c r="G9" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="6">
+        <v>10</v>
+      </c>
       <c r="I9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="8"/>
+      <c r="K9" s="8">
+        <v>10</v>
+      </c>
       <c r="L9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="N9" s="10"/>
+      <c r="N9" s="10">
+        <v>10</v>
+      </c>
       <c r="O9" s="11" t="s">
         <v>29</v>
       </c>
       <c r="P9" t="str">
         <f>IF(N9="","-",IF(ISNUMBER(N9),IF(N9&gt;10,"TAK – dodaj ciezar (hantle)","NIE – zostan z ciezarem"),"-"))</f>
-        <v>-</v>
+        <v>NIE – zostan z ciezarem</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>30</v>
@@ -1005,27 +1017,33 @@
       <c r="G10" s="6">
         <v>55</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="6">
+        <v>12</v>
+      </c>
       <c r="I10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="8">
         <v>60</v>
       </c>
-      <c r="K10" s="8"/>
+      <c r="K10" s="8">
+        <v>12</v>
+      </c>
       <c r="L10" s="9" t="s">
         <v>34</v>
       </c>
       <c r="M10" s="10">
         <v>65</v>
       </c>
-      <c r="N10" s="10"/>
+      <c r="N10" s="10">
+        <v>12</v>
+      </c>
       <c r="O10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="P10" t="str">
         <f>IF(N10="","-",IF(ISNUMBER(N10),IF(N10&gt;12,"TAK – dodaj 2,5 kg","NIE – zostan z ciezarem"),"-"))</f>
-        <v>-</v>
+        <v>NIE – zostan z ciezarem</v>
       </c>
       <c r="Q10" s="12" t="s">
         <v>36</v>
@@ -1053,27 +1071,33 @@
       <c r="G11" s="6">
         <v>27.5</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="6">
+        <v>10</v>
+      </c>
       <c r="I11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="J11" s="8">
         <v>27.5</v>
       </c>
-      <c r="K11" s="8"/>
+      <c r="K11" s="8">
+        <v>11</v>
+      </c>
       <c r="L11" s="9" t="s">
         <v>34</v>
       </c>
       <c r="M11" s="10">
         <v>27.5</v>
       </c>
-      <c r="N11" s="10"/>
+      <c r="N11" s="10">
+        <v>12</v>
+      </c>
       <c r="O11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="P11" t="str">
         <f>IF(N11="","-",IF(ISNUMBER(N11),IF(N11&gt;12,"TAK – dodaj 1 kg","NIE – zostan z ciezarem"),"-"))</f>
-        <v>-</v>
+        <v>NIE – zostan z ciezarem</v>
       </c>
       <c r="Q11" s="12" t="s">
         <v>37</v>
@@ -1101,27 +1125,33 @@
       <c r="G12" s="6">
         <v>7.5</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="6">
+        <v>12</v>
+      </c>
       <c r="I12" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J12" s="8">
-        <v>7.5</v>
-      </c>
-      <c r="K12" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="K12" s="8">
+        <v>14</v>
+      </c>
       <c r="L12" s="9" t="s">
         <v>40</v>
       </c>
       <c r="M12" s="10">
         <v>7.5</v>
       </c>
-      <c r="N12" s="10"/>
+      <c r="N12" s="10">
+        <v>12</v>
+      </c>
       <c r="O12" s="11" t="s">
         <v>41</v>
       </c>
       <c r="P12" t="str">
         <f>IF(N12="","-",IF(ISNUMBER(N12),IF(N12&gt;15,"TAK – dodaj 1 kg","NIE – zostan z ciezarem"),"-"))</f>
-        <v>-</v>
+        <v>NIE – zostan z ciezarem</v>
       </c>
       <c r="Q12" s="12" t="s">
         <v>42</v>
@@ -1149,14 +1179,18 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="6">
+        <v>25</v>
+      </c>
       <c r="I13" s="7">
         <v>25</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="8"/>
+      <c r="K13" s="8">
+        <v>25</v>
+      </c>
       <c r="L13" s="9">
         <v>25</v>
       </c>
@@ -1165,7 +1199,7 @@
       <c r="O13" s="16"/>
       <c r="P13" t="str">
         <f>IF(K13="","-",IF(ISNUMBER(K13),IF(K13&gt;15,"TAK – zwieksz czas","NIE – zostan z czasem"),"-"))</f>
-        <v>-</v>
+        <v>TAK – zwieksz czas</v>
       </c>
       <c r="Q13" s="12" t="s">
         <v>45</v>
